--- a/The List.xlsx
+++ b/The List.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pfi-s\OneDrive\Documentos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pfi-s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3E5E73A-161E-4C71-8325-74AF16173E2C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57841D5E-7B79-44D1-863A-40DBC6D54D73}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{794630E7-8E2D-43F1-8183-E92CABA8AB98}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
   <si>
     <t>Mario &amp; Luigi: Superstar Saga</t>
   </si>
@@ -91,6 +91,12 @@
   </si>
   <si>
     <t>Wifi Required</t>
+  </si>
+  <si>
+    <t>Language Level</t>
+  </si>
+  <si>
+    <t>Scores are given in an scale of 0: none to 10: Ultra diffcult</t>
   </si>
 </sst>
 </file>
@@ -126,8 +132,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -442,13 +449,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7643A02E-E778-4DEF-9EFE-E7C741A60671}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.28515625" customWidth="1"/>
+    <col min="17" max="17" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -494,8 +502,11 @@
       <c r="O1" t="s">
         <v>21</v>
       </c>
+      <c r="P1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -540,6 +551,12 @@
       </c>
       <c r="O2" t="s">
         <v>18</v>
+      </c>
+      <c r="P2" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
